--- a/data/trans_camb/P2C_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 21,36</t>
+          <t>10,49; 21,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 9,82</t>
+          <t>-1,04; 9,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,96; -7,19</t>
+          <t>-17,53; -6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 30,55</t>
+          <t>18,28; 30,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 17,01</t>
+          <t>4,85; 16,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -5,86</t>
+          <t>-17,64; -6,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,82; 24,26</t>
+          <t>15,19; 23,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 11,34</t>
+          <t>3,82; 11,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -8,66</t>
+          <t>-16,05; -8,71</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,75; 128,26</t>
+          <t>48,22; 129,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 57,47</t>
+          <t>-5,75; 57,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,81; -39,02</t>
+          <t>-81,65; -39,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,25; 164,3</t>
+          <t>75,4; 168,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,38; 88,74</t>
+          <t>20,84; 91,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,41; -28,69</t>
+          <t>-73,83; -31,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,61; 129,56</t>
+          <t>68,86; 129,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,0; 62,53</t>
+          <t>18,08; 63,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,64; -45,07</t>
+          <t>-74,23; -45,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 14,75</t>
+          <t>4,35; 14,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,92</t>
+          <t>3,19; 13,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,86; -12,26</t>
+          <t>-22,84; -11,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 21,3</t>
+          <t>9,29; 21,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 12,55</t>
+          <t>0,88; 12,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,29; -27,28</t>
+          <t>-41,27; -27,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 16,37</t>
+          <t>8,11; 16,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,05</t>
+          <t>4,16; 11,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-28,77; -20,24</t>
+          <t>-28,62; -20,2</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,83; 54,08</t>
+          <t>13,83; 54,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 51,17</t>
+          <t>9,76; 50,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,17; -42,55</t>
+          <t>-72,19; -42,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 44,64</t>
+          <t>17,32; 43,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 25,93</t>
+          <t>1,63; 25,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,27; -55,21</t>
+          <t>-78,79; -56,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,53; 43,23</t>
+          <t>19,57; 43,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 32,18</t>
+          <t>10,0; 31,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,39; -53,0</t>
+          <t>-70,53; -52,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,75; 23,82</t>
+          <t>13,19; 24,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 6,04</t>
+          <t>-4,6; 6,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,33; -29,36</t>
+          <t>-40,33; -29,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 27,56</t>
+          <t>18,0; 27,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 11,89</t>
+          <t>1,84; 12,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,38; -32,16</t>
+          <t>-43,86; -31,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 24,22</t>
+          <t>17,34; 24,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 7,47</t>
+          <t>-0,73; 7,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-40,17; -32,22</t>
+          <t>-39,81; -32,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,24; 45,98</t>
+          <t>22,63; 46,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 11,58</t>
+          <t>-7,89; 13,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,86; -55,2</t>
+          <t>-70,03; -56,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,81; 49,68</t>
+          <t>29,13; 49,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 21,26</t>
+          <t>2,98; 22,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,33; -56,92</t>
+          <t>-73,18; -56,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,8; 44,0</t>
+          <t>29,11; 44,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 13,46</t>
+          <t>-1,21; 13,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,14; -58,49</t>
+          <t>-68,34; -58,09</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,64; 25,69</t>
+          <t>14,06; 26,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 3,67</t>
+          <t>-7,21; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -16,23</t>
+          <t>-30,12; -16,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,08; 25,61</t>
+          <t>13,4; 25,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 11,5</t>
+          <t>0,39; 11,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -7,09</t>
+          <t>-16,16; -7,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,84; 23,93</t>
+          <t>15,51; 24,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 5,74</t>
+          <t>-1,74; 5,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,01; -13,49</t>
+          <t>-22,31; -13,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,32; 88,48</t>
+          <t>38,71; 93,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 12,39</t>
+          <t>-20,42; 16,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,47; -52,74</t>
+          <t>-86,43; -52,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51,9; 116,93</t>
+          <t>46,77; 109,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 51,45</t>
+          <t>0,94; 48,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,51; -31,09</t>
+          <t>-56,82; -31,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,81; 89,72</t>
+          <t>50,51; 92,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 21,77</t>
+          <t>-5,56; 22,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-76,4; -49,35</t>
+          <t>-75,12; -48,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 21,03</t>
+          <t>9,59; 20,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 6,34</t>
+          <t>-3,46; 5,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,69</t>
+          <t>-7,29; 0,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 10,2</t>
+          <t>-1,12; 10,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 0,76</t>
+          <t>-8,61; 1,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -4,09</t>
+          <t>-12,91; -4,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 14,04</t>
+          <t>5,73; 13,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,78</t>
+          <t>-4,92; 1,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -3,08</t>
+          <t>-9,15; -2,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>65,14; 225,17</t>
+          <t>63,71; 214,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 67,94</t>
+          <t>-24,45; 64,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 8,59</t>
+          <t>-49,53; 7,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 63,59</t>
+          <t>-5,62; 70,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 5,25</t>
+          <t>-40,99; 9,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,56; -26,44</t>
+          <t>-58,33; -26,36</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,58; 106,78</t>
+          <t>32,45; 101,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 12,94</t>
+          <t>-29,4; 14,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,93; -22,55</t>
+          <t>-51,32; -20,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7,56; 19,43</t>
+          <t>6,69; 18,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,52</t>
+          <t>-4,15; 5,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,93</t>
+          <t>-6,56; 1,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,59</t>
+          <t>2,18; 14,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,76</t>
+          <t>-6,23; 4,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 57,98</t>
+          <t>-7,62; 54,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,97</t>
+          <t>6,23; 14,96</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,56</t>
+          <t>-3,48; 3,73</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 45,3</t>
+          <t>-5,04; 48,45</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>54,29; 233,31</t>
+          <t>50,6; 231,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 67,9</t>
+          <t>-32,45; 71,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 22,74</t>
+          <t>-47,34; 22,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13,17; 102,8</t>
+          <t>10,17; 96,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 32,27</t>
+          <t>-30,8; 28,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 403,78</t>
+          <t>-40,93; 382,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,65; 121,53</t>
+          <t>38,82; 120,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 28,91</t>
+          <t>-21,99; 30,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 345,6</t>
+          <t>-33,78; 398,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,32; 22,65</t>
+          <t>6,35; 23,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 12,1</t>
+          <t>-2,67; 12,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 4,71</t>
+          <t>-6,54; 6,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16,6; 31,47</t>
+          <t>17,08; 31,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,07; 21,23</t>
+          <t>7,47; 22,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,23; 14,34</t>
+          <t>2,2; 14,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,2; 26,48</t>
+          <t>14,35; 25,72</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,99; 15,79</t>
+          <t>4,5; 15,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 9,38</t>
+          <t>0,38; 8,62</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>24,47; 130,98</t>
+          <t>24,0; 130,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 66,51</t>
+          <t>-10,25; 70,36</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 25,68</t>
+          <t>-24,78; 38,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62,84; 162,71</t>
+          <t>63,4; 165,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,73; 114,97</t>
+          <t>28,17; 116,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,42; 76,61</t>
+          <t>7,74; 74,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,58; 132,28</t>
+          <t>58,9; 134,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,01; 79,3</t>
+          <t>17,63; 75,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,49; 48,22</t>
+          <t>1,41; 42,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,96</t>
+          <t>13,2; 17,91</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,29</t>
+          <t>-0,05; 4,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-20,26; -15,32</t>
+          <t>-19,94; -14,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14,81; 19,48</t>
+          <t>14,8; 19,41</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,67</t>
+          <t>1,87; 6,83</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 2,2</t>
+          <t>-18,47; 1,43</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,06</t>
+          <t>14,74; 18,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,92</t>
+          <t>1,56; 4,89</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -6,23</t>
+          <t>-18,07; -8,1</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>42,97; 63,68</t>
+          <t>43,88; 64,65</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 15,29</t>
+          <t>-0,09; 16,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,55; -53,93</t>
+          <t>-67,86; -53,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40,97; 58,15</t>
+          <t>41,2; 57,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,62; 20,09</t>
+          <t>5,14; 20,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 6,55</t>
+          <t>-52,76; 4,24</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,71; 58,58</t>
+          <t>44,76; 58,34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,87</t>
+          <t>4,8; 15,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-56,45; -19,62</t>
+          <t>-56,4; -25,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-12,62</t>
+          <t>-11,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,77</t>
+          <t>-9,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-10,6</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 21,39</t>
+          <t>10,03; 21,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,93</t>
+          <t>-1,71; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,53; -6,91</t>
+          <t>-16,26; -6,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 30,7</t>
+          <t>18,44; 30,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 16,88</t>
+          <t>4,72; 17,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -6,26</t>
+          <t>-15,64; -3,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,19; 23,95</t>
+          <t>15,77; 23,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,45</t>
+          <t>3,32; 11,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -8,71</t>
+          <t>-14,15; -5,93</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-66,33%</t>
+          <t>-59,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-55,95%</t>
+          <t>-46,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-61,7%</t>
+          <t>-53,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,22; 129,31</t>
+          <t>47,91; 132,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 57,0</t>
+          <t>-7,79; 57,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,65; -39,81</t>
+          <t>-76,3; -31,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,4; 168,18</t>
+          <t>77,61; 169,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,84; 91,87</t>
+          <t>20,33; 93,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,83; -31,13</t>
+          <t>-68,21; -19,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,86; 129,4</t>
+          <t>71,47; 131,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,08; 63,59</t>
+          <t>14,79; 60,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,23; -45,48</t>
+          <t>-65,52; -31,45</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-17,82</t>
+          <t>-16,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-33,1</t>
+          <t>-29,79</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-24,29</t>
+          <t>-21,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 14,57</t>
+          <t>4,89; 14,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,86</t>
+          <t>3,27; 14,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -11,63</t>
+          <t>-21,37; -9,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 21,04</t>
+          <t>9,75; 20,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 12,46</t>
+          <t>1,04; 11,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,27; -27,8</t>
+          <t>-35,2; -23,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,18</t>
+          <t>8,34; 16,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,94</t>
+          <t>4,24; 12,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-28,62; -20,2</t>
+          <t>-25,95; -18,08</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-60,18%</t>
+          <t>-54,43%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-64,56%</t>
+          <t>-58,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-61,38%</t>
+          <t>-55,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,83; 54,14</t>
+          <t>14,91; 51,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 50,79</t>
+          <t>10,23; 50,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,19; -42,75</t>
+          <t>-67,46; -35,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 43,46</t>
+          <t>18,04; 42,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 25,73</t>
+          <t>1,87; 24,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,79; -56,3</t>
+          <t>-65,5; -49,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,57; 43,16</t>
+          <t>20,11; 43,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 31,82</t>
+          <t>10,4; 32,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,53; -52,98</t>
+          <t>-62,91; -47,5</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-35,06</t>
+          <t>-34,56</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-37,13</t>
+          <t>-34,84</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-36,13</t>
+          <t>-34,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 24,19</t>
+          <t>13,54; 24,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 6,81</t>
+          <t>-5,07; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,33; -29,79</t>
+          <t>-39,76; -29,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 27,53</t>
+          <t>17,45; 27,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 12,39</t>
+          <t>1,18; 12,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,86; -31,9</t>
+          <t>-40,08; -30,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 24,53</t>
+          <t>17,15; 24,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,21</t>
+          <t>-0,11; 7,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-39,81; -32,36</t>
+          <t>-38,22; -31,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-63,4%</t>
+          <t>-62,5%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-63,0%</t>
+          <t>-59,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-63,17%</t>
+          <t>-60,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,63; 46,89</t>
+          <t>23,2; 46,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 13,27</t>
+          <t>-8,75; 11,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,03; -56,31</t>
+          <t>-68,85; -55,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,13; 49,63</t>
+          <t>28,18; 49,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 22,33</t>
+          <t>1,91; 22,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,18; -56,62</t>
+          <t>-64,95; -53,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,11; 44,61</t>
+          <t>28,89; 44,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 13,24</t>
+          <t>-0,19; 13,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,34; -58,09</t>
+          <t>-64,89; -55,59</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-22,31</t>
+          <t>-17,59</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-11,44</t>
+          <t>-10,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-17,1</t>
+          <t>-13,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,06; 26,46</t>
+          <t>14,4; 26,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 4,54</t>
+          <t>-6,79; 4,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-30,12; -16,61</t>
+          <t>-22,43; -12,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,4; 25,1</t>
+          <t>14,17; 25,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 11,21</t>
+          <t>0,88; 11,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -7,28</t>
+          <t>-14,62; -5,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 24,07</t>
+          <t>15,84; 23,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 5,93</t>
+          <t>-1,66; 6,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-22,31; -13,03</t>
+          <t>-17,18; -10,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-69,07%</t>
+          <t>-54,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-45,27%</t>
+          <t>-39,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-59,37%</t>
+          <t>-47,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,71; 93,76</t>
+          <t>41,55; 89,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 16,12</t>
+          <t>-19,94; 17,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,43; -52,68</t>
+          <t>-64,01; -43,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46,77; 109,17</t>
+          <t>49,96; 115,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 48,52</t>
+          <t>3,27; 52,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,82; -31,98</t>
+          <t>-50,97; -25,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,51; 92,18</t>
+          <t>51,09; 90,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 22,43</t>
+          <t>-5,39; 22,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,12; -48,38</t>
+          <t>-55,46; -39,69</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,25</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,36</t>
+          <t>-8,09</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-5,75</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,59; 20,15</t>
+          <t>9,38; 20,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,9</t>
+          <t>-3,89; 5,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,58</t>
+          <t>-7,33; 0,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 10,83</t>
+          <t>-1,15; 10,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 1,35</t>
+          <t>-9,53; 0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -4,16</t>
+          <t>-12,38; -4,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,86</t>
+          <t>5,7; 13,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 1,93</t>
+          <t>-4,94; 1,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -2,8</t>
+          <t>-8,48; -2,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-26,69%</t>
+          <t>-27,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-44,69%</t>
+          <t>-43,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-38,11%</t>
+          <t>-37,51%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>63,71; 214,15</t>
+          <t>61,11; 226,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 64,17</t>
+          <t>-27,64; 62,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 7,47</t>
+          <t>-50,08; 7,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 70,76</t>
+          <t>-5,85; 64,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 9,58</t>
+          <t>-44,79; 3,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,33; -26,36</t>
+          <t>-56,5; -25,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,45; 101,44</t>
+          <t>33,14; 99,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 14,41</t>
+          <t>-29,26; 14,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,32; -20,76</t>
+          <t>-49,06; -21,53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,96</t>
+          <t>-5,54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,75</t>
+          <t>-3,99</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,69; 18,98</t>
+          <t>6,9; 19,25</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 5,5</t>
+          <t>-4,17; 5,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,67</t>
+          <t>-6,09; 2,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,18; 14,47</t>
+          <t>2,43; 14,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 4,25</t>
+          <t>-5,67; 5,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 54,36</t>
+          <t>-10,46; -0,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,96</t>
+          <t>6,38; 14,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,73</t>
+          <t>-3,65; 3,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 48,45</t>
+          <t>-7,1; -0,95</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-19,07%</t>
+          <t>-19,16%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>137,12%</t>
+          <t>-31,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>103,29%</t>
+          <t>-27,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>50,6; 231,04</t>
+          <t>52,62; 235,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 71,67</t>
+          <t>-31,22; 70,8</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 22,75</t>
+          <t>-46,86; 25,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,17; 96,49</t>
+          <t>11,85; 95,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 28,47</t>
+          <t>-28,73; 34,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 382,8</t>
+          <t>-49,44; -6,31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,82; 120,32</t>
+          <t>38,97; 119,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 30,06</t>
+          <t>-23,31; 31,61</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-33,78; 398,05</t>
+          <t>-43,28; -7,82</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,03</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>4,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,35; 23,52</t>
+          <t>6,3; 23,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 12,74</t>
+          <t>-3,08; 11,48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 6,44</t>
+          <t>-8,12; 5,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17,08; 31,67</t>
+          <t>16,58; 30,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,47; 22,27</t>
+          <t>6,26; 21,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,2; 14,4</t>
+          <t>2,43; 14,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,35; 25,72</t>
+          <t>15,34; 26,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,5; 15,31</t>
+          <t>4,92; 15,7</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 8,62</t>
+          <t>0,38; 9,08</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-3,52%</t>
+          <t>-6,28%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>24,0; 130,53</t>
+          <t>25,74; 126,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 70,36</t>
+          <t>-12,99; 60,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 38,01</t>
+          <t>-31,07; 27,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>63,4; 165,64</t>
+          <t>61,64; 166,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>28,17; 116,74</t>
+          <t>23,2; 111,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,74; 74,9</t>
+          <t>7,95; 75,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,9; 134,93</t>
+          <t>57,85; 131,71</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,63; 75,97</t>
+          <t>18,8; 80,87</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,41; 42,95</t>
+          <t>1,18; 46,94</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-15,6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-13,16</t>
+          <t>-16,5</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-15,07</t>
+          <t>-16,03</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>13,2; 17,91</t>
+          <t>13,37; 17,95</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,53</t>
+          <t>-0,15; 4,51</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,94; -14,99</t>
+          <t>-17,47; -13,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,41</t>
+          <t>14,45; 19,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,83</t>
+          <t>1,73; 6,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-18,47; 1,43</t>
+          <t>-18,44; -14,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,19</t>
+          <t>14,77; 18,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,89</t>
+          <t>1,38; 4,67</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -8,1</t>
+          <t>-17,53; -14,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-59,07%</t>
+          <t>-53,51%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-38,12%</t>
+          <t>-47,79%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-47,26%</t>
+          <t>-50,28%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>43,88; 64,65</t>
+          <t>44,03; 63,77</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 16,13</t>
+          <t>-0,46; 16,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,86; -53,66</t>
+          <t>-58,05; -48,38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41,2; 57,95</t>
+          <t>40,18; 57,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,14; 20,41</t>
+          <t>4,78; 19,03</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 4,24</t>
+          <t>-51,72; -42,9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,76; 58,34</t>
+          <t>45,14; 58,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>4,8; 15,76</t>
+          <t>3,98; 14,9</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-56,4; -25,65</t>
+          <t>-53,51; -47,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R2-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
